--- a/NADA.xlsx
+++ b/NADA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ad1b5577dde8d52/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{B1951900-8AD9-4485-A4B0-BBF070F4B3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54F0E674-295A-43E2-9DDD-E3F9DA74A4F0}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{B1951900-8AD9-4485-A4B0-BBF070F4B3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CA986A6-482E-4F9D-9D22-93D0C5534AB7}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B04A2322-5056-4CED-A53E-C76B1B4F9AC6}"/>
   </bookViews>
@@ -36,12 +36,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>XCCVSV BDFJVBDFJKV}}</t>
   </si>
   <si>
     <t>FGNAGN</t>
+  </si>
+  <si>
+    <t>nrnhn46n6y67</t>
+  </si>
+  <si>
+    <t>uk46ukuyhn</t>
   </si>
   <si>
     <t>cbxcbfb</t>
@@ -416,22 +422,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A551E7-B603-4FF8-8ECF-FB663EE4804A}">
-  <dimension ref="B1:B8"/>
+  <dimension ref="B1:E8"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="2:5">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:2">
+    <row r="2" spans="2:5">
       <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:2">
+    <row r="6" spans="2:5">
+      <c r="E6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
       <c r="B8" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
